--- a/TestData/SeleniumTestData.xlsx
+++ b/TestData/SeleniumTestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mages\eclipse-workspace\CapstoneProject\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E10F03F9-E2F8-4B16-9D1F-D85775027DFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BED44DF2-4889-4645-A80A-BB01F017645B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -96,12 +96,6 @@
     <t>Todos id</t>
   </si>
   <si>
-    <t>`233215</t>
-  </si>
-  <si>
-    <t>`8078407</t>
-  </si>
-  <si>
     <t>`8884900039</t>
   </si>
   <si>
@@ -109,6 +103,12 @@
   </si>
   <si>
     <t>Android</t>
+  </si>
+  <si>
+    <t>`238257</t>
+  </si>
+  <si>
+    <t>`8106643</t>
   </si>
 </sst>
 </file>
@@ -657,10 +657,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
         <v>3</v>
@@ -704,13 +704,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>8</v>
